--- a/human_validation/judge/kor/judge_D014_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S005_P003__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,208 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생입니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제 인생의 가장 좋은 시절은 이미 지나갔다는 느낌이 계속 들어요. 그렇게 극적인 건 아닌데, 아무리 계획을 세우고 규율을 지키려 해도 다시 예전의 저 자신처럼 느껴지지 않을 거라는 완고한 느낌이 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 느껴오셨나요—몇 주 정도인가요, 아니면 몇 달에서 몇 년쯤 되나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 몇 년에 더 가까워요. 등산하다가 다친 이후로 시작됐어요—그러니까 지금으로부터 3년이 조금 넘었네요, 한 3년 3개월쯤이요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 이 3년 동안, 이 낮고 낙담한 느낌이 거의 매일 있었나요, 아니면 완전히 평소의 자신으로 느껴졌던 몇 주나 몇 달의 시기가 있었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 거의 매일이었던 것 같아요. 울고 그러는 건 아니지만, 작업실에 있을 때나 아내랑 저녁 먹을 때도 모든 것 밑에 이 낮고 회색빛 느낌이 깔려 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이 3년 동안, 기분이나 에너지가 이 평소 기준선보다 눈에 띄게 더 떨어진 2주 이상의 기간—뚜렷하게 더 나빠진 시기—이 있었나요, 아니면 그 기간 내내 거의 같은 수준으로 유지됐나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 대부분 너무 오랫동안 같은 낮은 수준으로 느껴져서, 분명하게 더 나빴던 별개의 시기를 딱 짚을 수 있을지 모르겠어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 이 낮은 기분과 함께, 수면, 식욕, 에너지, 집중력, 자존감 등에서 거의 매일, 2주 이상 함께 나타나는 변화들도 알아차리셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네—피로감은 꽤 지속적이에요. 여전히 일어나서 장을 보고 소소한 프로젝트를 하긴 하는데, 멘토링 세션을 준비하거나 지역사회 행사에 걸어가는 것만으로도 지쳐버려요. 낮잠을 자도 딱히 나아지지 않는 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 지난 3년 동안, 상황이 나아질 거라는 것에 대해 절망감을 자주 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네. 조용한 종류의 절망감이긴 한데, 분명히 있어요. 제 인생의 가장 좋은 시절이 이미 지나갔고, 아무리 계획하고 규율을 지켜도 다시 예전의 저처럼 느껴지지 못할 거라는 느낌이 들기 시작했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 지속성 우울장애 (D014) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 지난 3년 동안, 수면에 일관된 변화—잠들거나 계속 자는 데 어려움을 겪거나, 평소보다 훨씬 많이 자는 것 같은 변화—를 알아차리셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 수면에 일관된 변화를 알아차린 것 같지는 않아요, 없었어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지난 3년 동안, 식욕에 일관된 변화—평소보다 훨씬 적게 먹거나 훨씬 많이 먹는 것—를 알아차리셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 식욕에 일관된 변화는 딱히 알아차리지 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사 질문] 지난 3년 동안, 일상적인 일에서도 지속적으로 집중하거나 결정을 내리는 데 어려움을 겪으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 환자 응답] 그런 것 같지 않아요. 집중하거나 일상적인 결정을 내리는 데 지속적인 문제를 알아차리지 못했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>[9번째 턴 · 의사의 감별진단] 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>진단명: 지속성 우울장애 (D014)
 인구통계: 성별 남성 / 나이 65 / 직업상태 not in workforce / 최종학력 대학원 졸업
@@ -575,257 +768,33 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S083
-배경 서술: 브래드의 경과는 등산 도중 입은 심각한 부상으로 인해 STEM 멘토링, 예술 활동, 체스, 지역사회 행사를 중심으로 쌓아온 활동적이고 프로젝트로 가득했던 은퇴 생활을 대폭 줄여야 했던 시점에서 시작되었다. 그는 처음에는 특유의 공학도다운 절제력으로 적응해 나갔지만, 3년 3개월에 걸쳐 지속적인 우울한 기분, 휴식으로도 풀리지 않는 피로감, 나이 드는 것에 대한 조용한 절망감이 점차 워크숍, 잼 세션, 여행 계획에 대한 그의 참여를 좁혀놓았다. 그는 여전히 기본적인 일상과 일부 창작 활동을 유지했기 때문에 손상은 비교적 경미한 편이었지만, 그의 아내와 1차 진료의 둘 다 그가 오랫동안 유지해온 평소 수준보다 낮게 기능하고 있다는 것을 알아차렸다. 그는 정기 진료 방문 때 스스로 이 문제를 제기하고 평가 의뢰를 수락하면서 정신과 진료를 받게 되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 저는 스미스 선생입니다. 오늘 어떤 일로 저를 찾아오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제 인생의 가장 좋은 시절은 이미 지나갔다는 느낌이 계속 들어요. 그렇게 극적인 건 아닌데, 아무리 계획을 세우고 규율을 지키려 해도 다시 예전의 저 자신처럼 느껴지지 않을 거라는 완고한 느낌이 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이런 느낌을 얼마나 오래 느껴오셨나요—몇 주 정도인가요, 아니면 몇 달에서 몇 년쯤 되나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 몇 년에 더 가까워요. 등산하다가 다친 이후로 시작됐어요—그러니까 지금으로부터 3년이 조금 넘었네요, 한 3년 3개월쯤이요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 지속성 우울장애 (D014)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 이 3년 동안, 이 낮고 낙담한 느낌이 거의 매일 있었나요, 아니면 완전히 평소의 자신으로 느껴졌던 몇 주나 몇 달의 시기가 있었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 거의 매일이었던 것 같아요. 울고 그러는 건 아니지만, 작업실에 있을 때나 아내랑 저녁 먹을 때도 모든 것 밑에 이 낮고 회색빛 느낌이 깔려 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이 3년 동안, 기분이나 에너지가 이 평소 기준선보다 눈에 띄게 더 떨어진 2주 이상의 기간—뚜렷하게 더 나빠진 시기—이 있었나요, 아니면 그 기간 내내 거의 같은 수준으로 유지됐나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 대부분 너무 오랫동안 같은 낮은 수준으로 느껴져서, 분명하게 더 나빴던 별개의 시기를 딱 짚을 수 있을지 모르겠어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 이 낮은 기분과 함께, 수면, 식욕, 에너지, 집중력, 자존감 등에서 거의 매일, 2주 이상 함께 나타나는 변화들도 알아차리셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네—피로감은 꽤 지속적이에요. 여전히 일어나서 장을 보고 소소한 프로젝트를 하긴 하는데, 멘토링 세션을 준비하거나 지역사회 행사에 걸어가는 것만으로도 지쳐버려요. 낮잠을 자도 딱히 나아지지 않는 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 지난 3년 동안, 상황이 나아질 거라는 것에 대해 절망감을 자주 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네. 조용한 종류의 절망감이긴 한데, 분명히 있어요. 제 인생의 가장 좋은 시절이 이미 지나갔고, 아무리 계획하고 규율을 지켜도 다시 예전의 저처럼 느껴지지 못할 거라는 느낌이 들기 시작했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 지속성 우울장애 (D014) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 지난 3년 동안, 수면에 일관된 변화—잠들거나 계속 자는 데 어려움을 겪거나, 평소보다 훨씬 많이 자는 것 같은 변화—를 알아차리셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 수면에 일관된 변화를 알아차린 것 같지는 않아요, 없었어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지난 3년 동안, 식욕에 일관된 변화—평소보다 훨씬 적게 먹거나 훨씬 많이 먹는 것—를 알아차리셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 식욕에 일관된 변화는 딱히 알아차리지 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사의 감별진단] 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 의사 질문] 지난 3년 동안, 일상적인 일에서도 지속적으로 집중하거나 결정을 내리는 데 어려움을 겪으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>[9번째 턴 · 환자 응답] 그런 것 같지 않아요. 집중하거나 일상적인 결정을 내리는 데 지속적인 문제를 알아차리지 못했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
+배경 서술: 브래드의 경과는 등산 도중 입은 심각한 부상으로 인해 STEM 멘토링, 예술 활동, 체스, 지역사회 행사를 중심으로 쌓아온 활동적이고 프로젝트로 가득했던 은퇴 생활을 대폭 줄여야 했던 시점에서 시작되었다. 그는 처음에는 특유의 공학도다운 절제력으로 적응해 나갔지만, 3년 3개월에 걸쳐 지속적인 우울한 기분, 휴식으로도 풀리지 않는 피로감, 나이 드는 것에 대한 조용한 절망감이 점차 워크숍, 잼 세션, 여행 계획에 대한 그의 참여를 좁혀놓았다. 그는 여전히 기본적인 일상과 일부 창작 활동을 유지했기 때문에 손상은 비교적 경미한 편이었지만, 그의 아내와 1차 진료의 둘 다 그가 오랫동안 유지해온 평소 수준보다 낮게 기능하고 있다는 것을 알아차렸다. 그는 정기 진료 방문 때 스스로 이 문제를 제기하고 평가 의뢰를 수락하면서 정신과 진료를 받게 되었다.
+표집된 증상 목록:
+  - S024 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - S029 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - S083 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>[9번째 턴 · 의사의 감별진단] 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010) | 배제됨: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 지속성 우울장애 (D014, ICD: F34.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.
-  누락: 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 낮은 자존감: 자신을 무능하거나 무가치하다고 평가하는 지속적인 경향, 만성적으로 낮은 자기평가.</t>
+          <t>의사의 최종 진단: 지속성 우울장애 (D014, ICD: F34.1)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: dysthymic_symptoms (관계=must_include, 요구개수=3, 충족개수=3, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.
+  - 절망감: 미래에 대한 희망이 없다는 절망적인 느낌.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S005_P003__claude-sonnet-5_kor.xlsx
@@ -754,6 +754,11 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -790,11 +795,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A43:B43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D014_S005_P003__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D014_S005_P003__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.25</v>
+        <v>0.413</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.8518</v>
+        <v>0.7963</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.3981</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.5868</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
